--- a/rk2/опрос.xlsx
+++ b/rk2/опрос.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\projects\когнитивный_опросник\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachernev/Desktop/ML_sem6/rk2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F50269BF-F83C-4A28-9B3C-2274D9B8E76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F173842E-3ACB-F14C-8265-0BA2A6D60E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16740" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Общие" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="262">
   <si>
     <t xml:space="preserve">Укажите Ваш ник: </t>
   </si>
@@ -847,6 +847,12 @@
   </si>
   <si>
     <t>1 курс магистратуры</t>
+  </si>
+  <si>
+    <t>colan1ch</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
 </sst>
 </file>
@@ -1194,69 +1200,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.5" customWidth="1"/>
+    <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>259</v>
       </c>
@@ -1269,65 +1287,95 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{918AEE82-4C32-4D2A-9A2C-54D9872A7860}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="86.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="132" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>210</v>
+      </c>
+      <c r="B11" s="4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1344,720 +1392,852 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E173C5B-E50E-4F81-BBE9-AFB745769212}">
   <dimension ref="A1:B133"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="101" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B29" s="3"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B32" s="3"/>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B35" s="3"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B38" s="3"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B41" s="3"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B44" s="3"/>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B47" s="3"/>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B50" s="3"/>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B53" s="3"/>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B56" s="3"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B59" s="3"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B62" s="3"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B65" s="3"/>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B68" s="3"/>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B71" s="3"/>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B74" s="3"/>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B80" s="3"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B89" s="3"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B95" s="3"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B98" s="3"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B101" s="3"/>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B104" s="3"/>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="107" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B107" s="3"/>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B110" s="3"/>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="113" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B113" s="3"/>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="116" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B116" s="3"/>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B117" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="119" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B119" s="3"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="122" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B122" s="3"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B125" s="3"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B127" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B128" s="3"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="131" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B131" s="3"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>89</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -2068,135 +2248,207 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F989497F-D6BF-4CC3-A9E8-65B7B268FB46}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="107.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="107.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>161</v>
+      </c>
+      <c r="B25" s="4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2213,165 +2465,255 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB8BAF45-89FF-4D2C-887E-5BC6BB2FE74E}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="100.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="100.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>192</v>
+      </c>
+      <c r="B31" s="4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2388,45 +2730,63 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E91E38A-7D3C-4D65-A1E4-7E8E37C351DE}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="116.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="116.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="152.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>199</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2443,105 +2803,159 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D67B5CE6-C8E4-4B48-8CA8-4CEDB71E21DE}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="103" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="150" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="128" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>228</v>
+      </c>
+      <c r="B19" s="4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2558,55 +2972,79 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0C88F6-2B28-4185-BB0F-D49EA4F040C8}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="85.42578125" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="85.5" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="158.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="158.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>237</v>
+      </c>
+      <c r="B9" s="4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2623,60 +3061,87 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BCE72C3-20E6-4F04-ABF1-4B11CAC5F129}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="111.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="1" max="1" width="111.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="159" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="159" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>247</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2693,35 +3158,47 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3D3211-A7D8-404C-A253-8CF8616578A2}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="115" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="4"/>
+    <col min="2" max="2" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>251</v>
+      </c>
+      <c r="B5" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
